--- a/InputData/land/FoFObE/na-Fraction of Forests Owned by Entity.xlsx
+++ b/InputData/land/FoFObE/na-Fraction of Forests Owned by Entity.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\land\FoFObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCSC\2021年\EI三期\EPS模型\更新数据\新建文件夹\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D0EA2B-02FF-453F-9596-BFD3D1EA0E4A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B4A01-1362-4903-95E9-6ED89F4A60F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="FoFObE" sheetId="3" r:id="rId3"/>
+    <sheet name="Data-new" sheetId="4" r:id="rId3"/>
+    <sheet name="FoFObE" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>FoFObE Fraction of Forests Owned by Entity</t>
   </si>
@@ -41,73 +31,97 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>National Forest</t>
-  </si>
-  <si>
-    <t>Other public</t>
-  </si>
-  <si>
-    <t>Forest industry</t>
-  </si>
-  <si>
-    <t>Other private</t>
-  </si>
-  <si>
-    <t>Timber land</t>
-  </si>
-  <si>
-    <t>Reserved forest</t>
-  </si>
-  <si>
-    <t>Other forest</t>
-  </si>
-  <si>
-    <t>U.S.</t>
-  </si>
-  <si>
-    <t>Ownership of Forest Land (million hectares)</t>
-  </si>
-  <si>
-    <t>U.S. Forest Service</t>
-  </si>
-  <si>
-    <t>U.S. Forest Facts and Historical Trends</t>
-  </si>
-  <si>
-    <t>http://www.fia.fs.fed.us/library/briefings-summaries-overviews/docs/ForestFactsMetric.pdf</t>
-  </si>
-  <si>
-    <t>Page 6</t>
-  </si>
-  <si>
     <t>government</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>The amount of government-owned forest is provided in the table.</t>
-  </si>
-  <si>
-    <t>We assume that all privately-owned forest used for timber land is owned</t>
-  </si>
-  <si>
-    <t>by industry, and half of the remaining privately-owned forest land is owned</t>
-  </si>
-  <si>
-    <t>by industry.  The remainder is owned by consumers.</t>
+    <t>Fraction of Forest Owned (dimensionless)</t>
+  </si>
+  <si>
+    <t>2014-2018</t>
+  </si>
+  <si>
+    <t>Forest Resources in China</t>
+  </si>
+  <si>
+    <t>http://english.forestry.gov.cn/index.php?option=com_content&amp;view=article&amp;id=2:forest-resources-in-china&amp;catid=10&amp;Itemid=134#:~:text=The%20forestland%20in%20China%20is,%2Downed%20forestland%2C%20of%20which%2C&amp;text=State%2Downed%20forestland%20is%20124,for%2040%25%20of%20the%20total%2C&amp;text=Collectively%2Downed%20forestland%20is%20186,for%2060%25%20of%20the%20total.&amp;text=Low%2Dquality%20forests%20take%20up%2013%25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The amount of collectively-owned forestland is provided in the inventory. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 8th national forest inventory </t>
+  </si>
+  <si>
+    <t>The amount of government-owned forest is provided in the inventory.</t>
+  </si>
+  <si>
+    <t>Page 33:</t>
+  </si>
+  <si>
+    <t>By the end of 2009, 64.7% of the total collective forest lands had been
+clarified the rights and contracted to the farmer households</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China’s Strategy and Financing
+For Forestry Sustainable Development </t>
+  </si>
+  <si>
+    <t>https://www.un.org/esa/forests/wp-content/uploads/2014/12/China_case_study.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source 1: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">We assume that 65% of collective-owned forestland was allocated to individual household, and the reminder is owned by industry. </t>
+  </si>
+  <si>
+    <t>Ownership of Forest Land (%)</t>
+  </si>
+  <si>
+    <t>State-owned</t>
+  </si>
+  <si>
+    <t>Collective -owned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    individual household share</t>
+  </si>
+  <si>
+    <t>remainder of collective-owned</t>
+  </si>
+  <si>
+    <t>nonenergy industries</t>
+  </si>
+  <si>
+    <t>labor and consumers</t>
   </si>
   <si>
     <t>foreign entities</t>
   </si>
   <si>
-    <t>labor and consumers</t>
-  </si>
-  <si>
-    <t>Fraction of Forest Owned (dimensionless)</t>
-  </si>
-  <si>
-    <t>domestic industries</t>
+    <t>electricity suppliers</t>
+  </si>
+  <si>
+    <t>coal suppliers</t>
+  </si>
+  <si>
+    <t>natural gas and petroleum suppliers</t>
+  </si>
+  <si>
+    <t>biomass and biofuel suppliers</t>
+  </si>
+  <si>
+    <t>other energy suppliers</t>
+  </si>
+  <si>
+    <t>【2019年整理】林业概况 - 百度文库 (baidu.com)</t>
+  </si>
+  <si>
+    <t>https://wenku.baidu.com/view/494ab4fc814d2b160b4e767f5acfa1c7ab008254.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -115,13 +129,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -129,7 +143,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,17 +151,30 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -173,17 +200,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -198,8 +231,57 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>90682</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>494425</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>56745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{208BA20C-9B3A-4DAD-99EF-7D87F5CCA789}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5257799" y="605032"/>
+          <a:ext cx="6218951" cy="2880713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -519,281 +601,710 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" s="1"/>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A15" s="1"/>
+      <c r="B15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1" location=":~:text=The%20forestland%20in%20China%20is,%2Downed%20forestland%2C%20of%20which%2C&amp;text=State%2Downed%20forestland%20is%20124,for%2040%25%20of%20the%20total%2C&amp;text=Collectively%2Downed%20forestland%20is%20186,for%2060%25%20of%20the%20total.&amp;text=Low%2Dquality%20forests%20take%20up%2013%25." display="http://english.forestry.gov.cn/index.php?option=com_content&amp;view=article&amp;id=2:forest-resources-in-china&amp;catid=10&amp;Itemid=134#:~:text=The%20forestland%20in%20China%20is,%2Downed%20forestland%2C%20of%20which%2C&amp;text=State%2Downed%20forestland%20is%20124,for%2040%25%20of%20the%20total%2C&amp;text=Collectively%2Downed%20forestland%20is%20186,for%2060%25%20of%20the%20total.&amp;text=Low%2Dquality%20forests%20take%20up%2013%25." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{2E5F09B6-A2F0-7842-9D5A-684191B87258}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B2" s="6"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="C5" s="12"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18">
-        <v>29</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="C6" s="12"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G23" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A2D4A44-008A-4CCC-8B33-F6FB815E416F}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="28.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2"/>
+      <c r="D10">
+        <v>28.54</v>
+      </c>
+      <c r="E10">
+        <f>D10/D12</f>
+        <v>0.47080171560541079</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="D11">
+        <v>32.08</v>
+      </c>
+      <c r="E11">
+        <f>D11/D12</f>
+        <v>0.52919828439458927</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="2"/>
+      <c r="D12">
+        <f>SUM(D10:D11)</f>
+        <v>60.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G23" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G23" r:id="rId1" xr:uid="{C3F96646-9BF0-4D0E-A8AD-2CD9EACB8955}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.875" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="27" x14ac:dyDescent="0.15">
       <c r="B1" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <f>Data!B3</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5">
+        <f>Data!B6*Data!B4</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="5">
-        <f>SUM(Data!B3,Data!B7)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>0.42384105960264901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" s="5">
+        <f>Data!B5*Data!B4</f>
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" s="5">
-        <f>SUM(Data!B11,Data!B16,Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>0.52814569536423839</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="5">
-        <f>(Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>4.8013245033112585E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <xsd:import namespace="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="15" nillable="true" ma:displayName="统一合规性策略属性" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="16" nillable="true" ma:displayName="统一合规性策略 UI 操作" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoTags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a06c533b-533a-4f75-b7db-110f073002e4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="共享对象:" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="共享对象详细信息" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7845865-14F6-4B76-A7F6-679B903CA7A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85776286-E7E3-43A3-B7F4-D4071C3D65E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{698B3869-6847-4E63-B1D5-60951BA544B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>